--- a/output/graficos_dimensiones/comunal_e_matricula_a_2018_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2018_coquimbo.xlsx
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:20</t>
+    <t xml:space="preserve">2026-09-10 01:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2018_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2018_coquimbo.xlsx
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:35</t>
+    <t xml:space="preserve">2026-09-18 11:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2018_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2018_coquimbo.xlsx
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:31</t>
+    <t xml:space="preserve">2026-09-23 15:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2018_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2018_coquimbo.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">La Higuera</t>
   </si>
   <si>
-    <t xml:space="preserve">Paiguano</t>
+    <t xml:space="preserve">Paihuano</t>
   </si>
   <si>
     <t xml:space="preserve">Vicuña</t>
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 15:35</t>
+    <t xml:space="preserve">2026-10-04 10:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2018_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2018_coquimbo.xlsx
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:47</t>
+    <t xml:space="preserve">2026-10-05 16:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -757,7 +757,7 @@
         <v>106.84</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>43.62</v>
+        <v>43.63</v>
       </c>
     </row>
     <row r="10">
